--- a/salidas/empresas/NEM.xlsx
+++ b/salidas/empresas/NEM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.86658477783203</v>
+        <v>41.86658096313477</v>
       </c>
       <c r="C2" t="n">
         <v>61.79999923706055</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>35.85079956054688</v>
+        <v>35.85078048706055</v>
       </c>
       <c r="C3" t="n">
         <v>52.91999816894531</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>35.21913528442383</v>
+        <v>35.21915435791016</v>
       </c>
       <c r="C4" t="n">
         <v>51.88999938964844</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>39.61050796508789</v>
+        <v>39.61048889160156</v>
       </c>
       <c r="C5" t="n">
         <v>58.36000061035156</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>35.39561080932617</v>
+        <v>35.39561462402344</v>
       </c>
       <c r="C6" t="n">
         <v>52.15000152587891</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>35.99346160888672</v>
+        <v>35.99347305297852</v>
       </c>
       <c r="C7" t="n">
         <v>52.93000030517578</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.83743286132812</v>
+        <v>34.83744812011719</v>
       </c>
       <c r="C8" t="n">
         <v>51.22999954223633</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>34.85103607177734</v>
+        <v>34.85104370117188</v>
       </c>
       <c r="C9" t="n">
         <v>51.25</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>29.12774848937988</v>
+        <v>29.12776565551758</v>
       </c>
       <c r="C10" t="n">
         <v>42.75</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>30.84473609924316</v>
+        <v>30.84475517272949</v>
       </c>
       <c r="C11" t="n">
         <v>45.27000045776367</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>30.79403305053711</v>
+        <v>30.79403114318848</v>
       </c>
       <c r="C14" t="n">
         <v>45.09999847412109</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>30.79403305053711</v>
+        <v>30.79403114318848</v>
       </c>
       <c r="C15" t="n">
         <v>45.09999847412109</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>28.7371940612793</v>
+        <v>28.73718452453613</v>
       </c>
       <c r="C16" t="n">
         <v>41.9900016784668</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>28.53871154785156</v>
+        <v>28.53873825073242</v>
       </c>
       <c r="C17" t="n">
         <v>41.70000076293945</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>27.84065818786621</v>
+        <v>27.84064102172852</v>
       </c>
       <c r="C18" t="n">
         <v>40.68000030517578</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>26.7966251373291</v>
+        <v>26.796630859375</v>
       </c>
       <c r="C19" t="n">
         <v>39.06000137329102</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>28.64207649230957</v>
+        <v>28.64208602905273</v>
       </c>
       <c r="C20" t="n">
         <v>41.75</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>28.99193954467773</v>
+        <v>28.99193572998047</v>
       </c>
       <c r="C21" t="n">
         <v>42.2599983215332</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>30.75924491882324</v>
+        <v>30.75923156738281</v>
       </c>
       <c r="C22" t="n">
         <v>44.72999954223633</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>35.00215148925781</v>
+        <v>35.00214767456055</v>
       </c>
       <c r="C23" t="n">
         <v>50.90000152587891</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>34.17007064819336</v>
+        <v>34.17006683349609</v>
       </c>
       <c r="C24" t="n">
         <v>49.68999862670898</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>33.64645385742188</v>
+        <v>33.64642715454102</v>
       </c>
       <c r="C25" t="n">
         <v>48.83000183105469</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>37.38109970092773</v>
+        <v>37.38111114501953</v>
       </c>
       <c r="C26" t="n">
         <v>54.25</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.27639007568359</v>
+        <v>31.27639961242676</v>
       </c>
       <c r="C28" t="n">
         <v>45.29999923706055</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>30.52383422851562</v>
+        <v>30.52383804321289</v>
       </c>
       <c r="C29" t="n">
         <v>44.20999908447266</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>36.08950805664062</v>
+        <v>36.08950424194336</v>
       </c>
       <c r="C31" t="n">
         <v>52.15999984741211</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>33.18352127075195</v>
+        <v>33.18352890014648</v>
       </c>
       <c r="C32" t="n">
         <v>47.95999908447266</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>31.20469665527344</v>
+        <v>31.20468521118164</v>
       </c>
       <c r="C33" t="n">
         <v>45.09999847412109</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>26.88065910339355</v>
+        <v>26.88067054748535</v>
       </c>
       <c r="C34" t="n">
         <v>38.7599983215332</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>18.26719665527344</v>
+        <v>18.2672061920166</v>
       </c>
       <c r="C35" t="n">
         <v>26.34000015258789</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>23.33680534362793</v>
+        <v>23.33680725097656</v>
       </c>
       <c r="C36" t="n">
         <v>33.65000152587891</v>
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>27.673828125</v>
+        <v>27.6738224029541</v>
       </c>
       <c r="C38" t="n">
         <v>39.77999877929688</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.96083450317383</v>
+        <v>28.9608211517334</v>
       </c>
       <c r="C39" t="n">
         <v>41.63000106811523</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>31.21895217895508</v>
+        <v>31.21894454956055</v>
       </c>
       <c r="C40" t="n">
         <v>44.7599983215332</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>28.06637001037598</v>
+        <v>28.06636238098145</v>
       </c>
       <c r="C41" t="n">
         <v>40.2400016784668</v>
@@ -1248,11 +1260,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>34.08556747436523</v>
+        <v>34.08556365966797</v>
       </c>
       <c r="C42" t="n">
         <v>48.86999893188477</v>
@@ -1273,11 +1285,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>28.56463813781738</v>
+        <v>28.56464004516602</v>
       </c>
       <c r="C43" t="n">
         <v>40.86999893188477</v>
@@ -1298,11 +1310,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>28.90012359619141</v>
+        <v>28.90011405944824</v>
       </c>
       <c r="C44" t="n">
         <v>41.34999847412109</v>
@@ -1323,11 +1335,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>28.08937835693359</v>
+        <v>28.08938980102539</v>
       </c>
       <c r="C45" t="n">
         <v>40.18999862670898</v>
@@ -1348,11 +1360,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>30.83646774291992</v>
+        <v>30.83647155761719</v>
       </c>
       <c r="C46" t="n">
         <v>44.02000045776367</v>
@@ -1373,11 +1385,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>30.44416999816895</v>
+        <v>30.44417190551758</v>
       </c>
       <c r="C47" t="n">
         <v>43.45999908447266</v>
@@ -1398,7 +1410,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1423,11 +1435,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.20199966430664</v>
+        <v>33.20198059082031</v>
       </c>
       <c r="C49" t="n">
         <v>47.31000137329102</v>
@@ -1448,11 +1460,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>30.07898139953613</v>
+        <v>30.07898712158203</v>
       </c>
       <c r="C50" t="n">
         <v>42.86000061035156</v>
@@ -1473,11 +1485,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>34.58452606201172</v>
+        <v>34.58451843261719</v>
       </c>
       <c r="C51" t="n">
         <v>49.27999877929688</v>
@@ -1498,11 +1510,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>35.81246948242188</v>
+        <v>35.81247711181641</v>
       </c>
       <c r="C52" t="n">
         <v>50.93000030517578</v>
@@ -1523,11 +1535,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>39.43380355834961</v>
+        <v>39.43379974365234</v>
       </c>
       <c r="C53" t="n">
         <v>56.08000183105469</v>
@@ -1548,11 +1560,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>37.84463882446289</v>
+        <v>37.84463119506836</v>
       </c>
       <c r="C54" t="n">
         <v>53.81999969482422</v>
@@ -1573,11 +1585,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>43.49125289916992</v>
+        <v>43.49126052856445</v>
       </c>
       <c r="C55" t="n">
         <v>61.7400016784668</v>
@@ -1598,11 +1610,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.37740325927734</v>
+        <v>39.37741088867188</v>
       </c>
       <c r="C56" t="n">
         <v>55.90000152587891</v>
@@ -1623,11 +1635,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>43.19540023803711</v>
+        <v>43.19538116455078</v>
       </c>
       <c r="C57" t="n">
         <v>61.31999969482422</v>
@@ -1648,11 +1660,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>44.35312652587891</v>
+        <v>44.35311508178711</v>
       </c>
       <c r="C58" t="n">
         <v>62.81000137329102</v>
@@ -1673,11 +1685,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>42.97612762451172</v>
+        <v>42.97613525390625</v>
       </c>
       <c r="C59" t="n">
         <v>60.86000061035156</v>
@@ -1698,11 +1710,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>41.54264450073242</v>
+        <v>41.54266357421875</v>
       </c>
       <c r="C60" t="n">
         <v>58.83000183105469</v>
@@ -1723,11 +1735,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>43.48322677612305</v>
+        <v>43.48324584960938</v>
       </c>
       <c r="C61" t="n">
         <v>61.43000030517578</v>
@@ -1748,11 +1760,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>38.98130035400391</v>
+        <v>38.98130416870117</v>
       </c>
       <c r="C62" t="n">
         <v>55.06999969482422</v>
@@ -1773,11 +1785,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>39.12286758422852</v>
+        <v>39.12285995483398</v>
       </c>
       <c r="C63" t="n">
         <v>55.27000045776367</v>
@@ -1802,11 +1814,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>38.74734115600586</v>
+        <v>38.74733734130859</v>
       </c>
       <c r="C64" t="n">
         <v>54.58000183105469</v>
@@ -1831,11 +1843,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>41.60830307006836</v>
+        <v>41.60830688476562</v>
       </c>
       <c r="C65" t="n">
         <v>58.61000061035156</v>
@@ -1860,11 +1872,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>40.16006851196289</v>
+        <v>40.16007232666016</v>
       </c>
       <c r="C66" t="n">
         <v>56.56999969482422</v>
@@ -1889,7 +1901,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1918,11 +1930,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>39.63128280639648</v>
+        <v>39.63126754760742</v>
       </c>
       <c r="C68" t="n">
         <v>55.61000061035156</v>
@@ -1947,11 +1959,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>44.62704849243164</v>
+        <v>44.62705612182617</v>
       </c>
       <c r="C69" t="n">
         <v>62.61999893188477</v>
@@ -1976,11 +1988,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>45.07195281982422</v>
+        <v>45.07196044921875</v>
       </c>
       <c r="C70" t="n">
         <v>62.95000076293945</v>
@@ -2005,11 +2017,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>47.85003280639648</v>
+        <v>47.85004425048828</v>
       </c>
       <c r="C71" t="n">
         <v>66.83000183105469</v>
@@ -2034,11 +2046,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>49.31782150268555</v>
+        <v>49.31781768798828</v>
       </c>
       <c r="C72" t="n">
         <v>68.87999725341797</v>
@@ -2063,11 +2075,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.1948127746582</v>
+        <v>43.19482421875</v>
       </c>
       <c r="C73" t="n">
         <v>60.0099983215332</v>
@@ -2092,11 +2104,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>44.25290298461914</v>
+        <v>44.25291442871094</v>
       </c>
       <c r="C74" t="n">
         <v>61.47999954223633</v>
@@ -2121,11 +2133,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>42.77734375</v>
+        <v>42.77733993530273</v>
       </c>
       <c r="C75" t="n">
         <v>59.43000030517578</v>
@@ -2150,7 +2162,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2179,7 +2191,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2208,11 +2220,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>34.15993881225586</v>
+        <v>34.15991973876953</v>
       </c>
       <c r="C78" t="n">
         <v>47.15999984741211</v>
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2266,11 +2278,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>32.43540573120117</v>
+        <v>32.43542098999023</v>
       </c>
       <c r="C80" t="n">
         <v>44.47000122070312</v>
@@ -2295,11 +2307,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>36.96485137939453</v>
+        <v>36.96484375</v>
       </c>
       <c r="C81" t="n">
         <v>50.68000030517578</v>
@@ -2324,11 +2336,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>41.14386367797852</v>
+        <v>41.14385604858398</v>
       </c>
       <c r="C82" t="n">
         <v>56.02000045776367</v>
@@ -2353,11 +2365,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>40.08625793457031</v>
+        <v>40.08625030517578</v>
       </c>
       <c r="C83" t="n">
         <v>54.58000183105469</v>
@@ -2382,11 +2394,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>34.58523178100586</v>
+        <v>34.58522415161133</v>
       </c>
       <c r="C84" t="n">
         <v>47.09000015258789</v>
@@ -2411,7 +2423,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2440,7 +2452,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2469,11 +2481,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>29.81943321228027</v>
+        <v>29.8194522857666</v>
       </c>
       <c r="C87" t="n">
         <v>40.29000091552734</v>
@@ -2498,11 +2510,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>31.34302520751953</v>
+        <v>31.3430347442627</v>
       </c>
       <c r="C88" t="n">
         <v>41.88999938964844</v>
@@ -2527,11 +2539,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>24.24239158630371</v>
+        <v>24.24239921569824</v>
       </c>
       <c r="C89" t="n">
         <v>32.40000152587891</v>
@@ -2556,11 +2568,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.64904594421387</v>
+        <v>25.64905548095703</v>
       </c>
       <c r="C90" t="n">
         <v>34.27999877929688</v>
@@ -2585,11 +2597,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>22.64157485961914</v>
+        <v>22.64158058166504</v>
       </c>
       <c r="C91" t="n">
         <v>29.95000076293945</v>
@@ -2614,11 +2626,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>22.67937469482422</v>
+        <v>22.67937660217285</v>
       </c>
       <c r="C92" t="n">
         <v>30</v>
@@ -2641,11 +2653,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>24.01745796203613</v>
+        <v>24.0174560546875</v>
       </c>
       <c r="C93" t="n">
         <v>31.77000045776367</v>
@@ -2668,7 +2680,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2695,11 +2707,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>20.77144622802734</v>
+        <v>20.77143859863281</v>
       </c>
       <c r="C95" t="n">
         <v>27.26000022888184</v>
@@ -2722,11 +2734,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>18.91984367370605</v>
+        <v>18.91984939575195</v>
       </c>
       <c r="C96" t="n">
         <v>24.82999992370605</v>
@@ -2749,11 +2761,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>17.69681167602539</v>
+        <v>17.69681739807129</v>
       </c>
       <c r="C97" t="n">
         <v>23.03000068664551</v>
@@ -2776,11 +2788,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>16.59797096252441</v>
+        <v>16.59796142578125</v>
       </c>
       <c r="C98" t="n">
         <v>21.60000038146973</v>
@@ -2803,11 +2815,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>17.87354850769043</v>
+        <v>17.87355041503906</v>
       </c>
       <c r="C99" t="n">
         <v>23.26000022888184</v>
@@ -2830,11 +2842,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>18.12369155883789</v>
+        <v>18.12369918823242</v>
       </c>
       <c r="C100" t="n">
         <v>23.44000053405762</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>19.19843864440918</v>
+        <v>19.19844055175781</v>
       </c>
       <c r="C101" t="n">
         <v>24.82999992370605</v>
@@ -2884,11 +2896,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>17.69844055175781</v>
+        <v>17.69843864440918</v>
       </c>
       <c r="C102" t="n">
         <v>22.88999938964844</v>
@@ -2911,11 +2923,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>19.69179534912109</v>
+        <v>19.69180107116699</v>
       </c>
       <c r="C103" t="n">
         <v>25.44000053405762</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>19.28156089782715</v>
+        <v>19.28156280517578</v>
       </c>
       <c r="C104" t="n">
         <v>24.90999984741211</v>
@@ -2965,11 +2977,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>20.96898460388184</v>
+        <v>20.96898078918457</v>
       </c>
       <c r="C105" t="n">
         <v>27.09000015258789</v>
@@ -2992,11 +3004,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>17.85947608947754</v>
+        <v>17.85947799682617</v>
       </c>
       <c r="C106" t="n">
         <v>23.04999923706055</v>
@@ -3019,11 +3031,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>14.53552532196045</v>
+        <v>14.5355224609375</v>
       </c>
       <c r="C107" t="n">
         <v>18.76000022888184</v>
@@ -3046,11 +3058,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>14.25659370422363</v>
+        <v>14.25659275054932</v>
       </c>
       <c r="C108" t="n">
         <v>18.39999961853027</v>
@@ -3073,11 +3085,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>14.66311168670654</v>
+        <v>14.66311454772949</v>
       </c>
       <c r="C109" t="n">
         <v>18.89999961853027</v>
@@ -3100,11 +3112,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>19.51202774047852</v>
+        <v>19.51202201843262</v>
       </c>
       <c r="C110" t="n">
         <v>25.14999961853027</v>
@@ -3127,7 +3139,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3156,11 +3168,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>16.86198043823242</v>
+        <v>16.86198616027832</v>
       </c>
       <c r="C112" t="n">
         <v>21.70999908447266</v>
@@ -3185,7 +3197,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3214,11 +3226,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>21.15708923339844</v>
+        <v>21.1570930480957</v>
       </c>
       <c r="C114" t="n">
         <v>27.23999977111816</v>
@@ -3243,11 +3255,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>18.16109657287598</v>
+        <v>18.16109848022461</v>
       </c>
       <c r="C115" t="n">
         <v>23.36000061035156</v>
@@ -3272,11 +3284,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>13.34871864318848</v>
+        <v>13.34871482849121</v>
       </c>
       <c r="C116" t="n">
         <v>17.17000007629395</v>
@@ -3301,11 +3313,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>13.27097129821777</v>
+        <v>13.27097320556641</v>
       </c>
       <c r="C117" t="n">
         <v>17.06999969482422</v>
@@ -3330,11 +3342,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>12.51345539093018</v>
+        <v>12.51345348358154</v>
       </c>
       <c r="C118" t="n">
         <v>16.06999969482422</v>
@@ -3359,11 +3371,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>15.1531982421875</v>
+        <v>15.15319442749023</v>
       </c>
       <c r="C119" t="n">
         <v>19.45999908447266</v>
@@ -3388,11 +3400,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>14.33557415008545</v>
+        <v>14.33557796478271</v>
       </c>
       <c r="C120" t="n">
         <v>18.40999984741211</v>
@@ -3417,11 +3429,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>14.02662181854248</v>
+        <v>14.02661991119385</v>
       </c>
       <c r="C121" t="n">
         <v>17.98999977111816</v>
@@ -3446,11 +3458,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>15.5626106262207</v>
+        <v>15.56260776519775</v>
       </c>
       <c r="C122" t="n">
         <v>19.95999908447266</v>
@@ -3475,11 +3487,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>20.13939476013184</v>
+        <v>20.13938903808594</v>
       </c>
       <c r="C123" t="n">
         <v>25.82999992370605</v>
@@ -3504,11 +3516,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>20.74371147155762</v>
+        <v>20.74371337890625</v>
       </c>
       <c r="C124" t="n">
         <v>26.57999992370605</v>
@@ -3533,11 +3545,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>27.29147338867188</v>
+        <v>27.29147148132324</v>
       </c>
       <c r="C125" t="n">
         <v>34.97000122070312</v>
@@ -3562,11 +3574,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>25.29358673095703</v>
+        <v>25.29358100891113</v>
       </c>
       <c r="C126" t="n">
         <v>32.40999984741211</v>
@@ -3591,11 +3603,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>30.55179023742676</v>
+        <v>30.55179977416992</v>
       </c>
       <c r="C127" t="n">
         <v>39.11999893188477</v>
@@ -3620,11 +3632,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>34.36295318603516</v>
+        <v>34.36296844482422</v>
       </c>
       <c r="C128" t="n">
         <v>44</v>
@@ -3649,11 +3661,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>29.86453819274902</v>
+        <v>29.86453056335449</v>
       </c>
       <c r="C129" t="n">
         <v>38.2400016784668</v>
@@ -3678,11 +3690,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>30.70359230041504</v>
+        <v>30.70358085632324</v>
       </c>
       <c r="C130" t="n">
         <v>39.29000091552734</v>
@@ -3707,11 +3719,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>28.94529342651367</v>
+        <v>28.94531440734863</v>
       </c>
       <c r="C131" t="n">
         <v>37.04000091552734</v>
@@ -3734,11 +3746,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>25.35057830810547</v>
+        <v>25.35057640075684</v>
       </c>
       <c r="C132" t="n">
         <v>32.43999862670898</v>
@@ -3761,11 +3773,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.6641788482666</v>
+        <v>26.66418266296387</v>
       </c>
       <c r="C133" t="n">
         <v>34.06999969482422</v>
@@ -3788,11 +3800,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>28.3937873840332</v>
+        <v>28.393798828125</v>
       </c>
       <c r="C134" t="n">
         <v>36.27999877929688</v>
@@ -3815,11 +3827,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>26.79722213745117</v>
+        <v>26.7972297668457</v>
       </c>
       <c r="C135" t="n">
         <v>34.2400016784668</v>
@@ -3842,11 +3854,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>25.83459854125977</v>
+        <v>25.83459091186523</v>
       </c>
       <c r="C136" t="n">
         <v>32.95999908447266</v>
@@ -3869,11 +3881,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>26.50082969665527</v>
+        <v>26.5008373260498</v>
       </c>
       <c r="C137" t="n">
         <v>33.81000137329102</v>
@@ -3896,11 +3908,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>26.76734352111816</v>
+        <v>26.7673397064209</v>
       </c>
       <c r="C138" t="n">
         <v>34.15000152587891</v>
@@ -3923,11 +3935,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>25.42538833618164</v>
+        <v>25.42538070678711</v>
       </c>
       <c r="C139" t="n">
         <v>32.38999938964844</v>
@@ -3950,7 +3962,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3977,11 +3989,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>30.09600067138672</v>
+        <v>30.09598731994629</v>
       </c>
       <c r="C141" t="n">
         <v>38.34000015258789</v>
@@ -4004,7 +4016,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4031,11 +4043,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>28.44036674499512</v>
+        <v>28.44037246704102</v>
       </c>
       <c r="C143" t="n">
         <v>36.15999984741211</v>
@@ -4060,11 +4072,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>29.09317207336426</v>
+        <v>29.09317398071289</v>
       </c>
       <c r="C144" t="n">
         <v>36.9900016784668</v>
@@ -4089,11 +4101,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>29.57193374633789</v>
+        <v>29.57192420959473</v>
       </c>
       <c r="C145" t="n">
         <v>37.52000045776367</v>
@@ -4118,11 +4130,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.92853546142578</v>
+        <v>31.92853736877441</v>
       </c>
       <c r="C146" t="n">
         <v>40.5099983215332</v>
@@ -4147,11 +4159,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>30.10787200927734</v>
+        <v>30.10788154602051</v>
       </c>
       <c r="C147" t="n">
         <v>38.20000076293945</v>
@@ -4174,11 +4186,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>30.90495300292969</v>
+        <v>30.90494155883789</v>
       </c>
       <c r="C148" t="n">
         <v>39.06999969482422</v>
@@ -4201,11 +4213,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>31.0789737701416</v>
+        <v>31.07897186279297</v>
       </c>
       <c r="C149" t="n">
         <v>39.29000091552734</v>
@@ -4230,11 +4242,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>30.79421043395996</v>
+        <v>30.79421424865723</v>
       </c>
       <c r="C150" t="n">
         <v>38.93000030517578</v>
@@ -4259,11 +4271,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>29.93788719177246</v>
+        <v>29.93790245056152</v>
       </c>
       <c r="C151" t="n">
         <v>37.70999908447266</v>
@@ -4288,11 +4300,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>29.12018203735352</v>
+        <v>29.12017059326172</v>
       </c>
       <c r="C152" t="n">
         <v>36.68000030517578</v>
@@ -4317,11 +4329,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>24.63465690612793</v>
+        <v>24.63465118408203</v>
       </c>
       <c r="C153" t="n">
         <v>31.03000068664551</v>
@@ -4346,7 +4358,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4375,11 +4387,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>24.66386222839355</v>
+        <v>24.66386032104492</v>
       </c>
       <c r="C155" t="n">
         <v>30.92000007629395</v>
@@ -4402,7 +4414,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4429,11 +4441,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>27.75415229797363</v>
+        <v>27.75414657592773</v>
       </c>
       <c r="C157" t="n">
         <v>34.65000152587891</v>
@@ -4456,11 +4468,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>27.32162857055664</v>
+        <v>27.32161521911621</v>
       </c>
       <c r="C158" t="n">
         <v>34.11000061035156</v>
@@ -4483,11 +4495,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>27.32963371276855</v>
+        <v>27.32962799072266</v>
       </c>
       <c r="C159" t="n">
         <v>34.11999893188477</v>
@@ -4512,11 +4524,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>28.76798820495605</v>
+        <v>28.76799392700195</v>
       </c>
       <c r="C160" t="n">
         <v>35.77000045776367</v>
@@ -4541,11 +4553,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>25.60289192199707</v>
+        <v>25.60288619995117</v>
       </c>
       <c r="C161" t="n">
         <v>31.05999946594238</v>
@@ -4570,11 +4582,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>27.2762279510498</v>
+        <v>27.27622413635254</v>
       </c>
       <c r="C162" t="n">
         <v>33.09000015258789</v>
@@ -4599,11 +4611,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>31.84071922302246</v>
+        <v>31.84071159362793</v>
       </c>
       <c r="C163" t="n">
         <v>38.47000122070312</v>
@@ -4628,11 +4640,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>30.22674942016602</v>
+        <v>30.22673988342285</v>
       </c>
       <c r="C164" t="n">
         <v>36.52000045776367</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>33.01601028442383</v>
+        <v>33.01600646972656</v>
       </c>
       <c r="C165" t="n">
         <v>39.88999938964844</v>
@@ -4682,11 +4694,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>31.50106811523438</v>
+        <v>31.50105667114258</v>
       </c>
       <c r="C166" t="n">
         <v>37.91999816894531</v>
@@ -4709,11 +4721,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>33.00467300415039</v>
+        <v>33.00468063354492</v>
       </c>
       <c r="C167" t="n">
         <v>39.72999954223633</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>31.89980697631836</v>
+        <v>31.89982414245605</v>
       </c>
       <c r="C168" t="n">
         <v>38.40000152587891</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>36.22374725341797</v>
+        <v>36.2237434387207</v>
       </c>
       <c r="C169" t="n">
         <v>43.45000076293945</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>37.56597900390625</v>
+        <v>37.56599426269531</v>
       </c>
       <c r="C170" t="n">
         <v>45.06000137329102</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>37.20750045776367</v>
+        <v>37.20750427246094</v>
       </c>
       <c r="C171" t="n">
         <v>44.63000106811523</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>37.85597610473633</v>
+        <v>37.85596466064453</v>
       </c>
       <c r="C172" t="n">
         <v>45.27999877929688</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>49.72775650024414</v>
+        <v>49.72776031494141</v>
       </c>
       <c r="C173" t="n">
         <v>59.47999954223633</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>48.88335800170898</v>
+        <v>48.88335037231445</v>
       </c>
       <c r="C174" t="n">
         <v>58.47000122070312</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>51.83886337280273</v>
+        <v>51.83887481689453</v>
       </c>
       <c r="C175" t="n">
         <v>61.7400016784668</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>58.10250854492188</v>
+        <v>58.10252380371094</v>
       </c>
       <c r="C176" t="n">
         <v>69.19999694824219</v>
@@ -4997,11 +5009,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>56.49042510986328</v>
+        <v>56.49043273925781</v>
       </c>
       <c r="C177" t="n">
         <v>67.27999877929688</v>
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>53.4779052734375</v>
+        <v>53.47791290283203</v>
       </c>
       <c r="C178" t="n">
         <v>63.45000076293945</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>52.96377944946289</v>
+        <v>52.96377563476562</v>
       </c>
       <c r="C179" t="n">
         <v>62.84000015258789</v>
@@ -5084,7 +5096,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>50.81629180908203</v>
+        <v>50.81630706787109</v>
       </c>
       <c r="C181" t="n">
         <v>59.88999938964844</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>50.57024002075195</v>
+        <v>50.57023239135742</v>
       </c>
       <c r="C182" t="n">
         <v>59.59999847412109</v>
@@ -5171,7 +5183,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5200,11 +5212,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>51.63875579833984</v>
+        <v>51.63874816894531</v>
       </c>
       <c r="C184" t="n">
         <v>60.27000045776367</v>
@@ -5229,11 +5241,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>53.4722900390625</v>
+        <v>53.47226715087891</v>
       </c>
       <c r="C185" t="n">
         <v>62.40999984741211</v>
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>62.95696258544922</v>
+        <v>62.95694732666016</v>
       </c>
       <c r="C186" t="n">
         <v>73.48000335693359</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>54.71026992797852</v>
+        <v>54.71028137207031</v>
       </c>
       <c r="C187" t="n">
         <v>63.38000106811523</v>
@@ -5316,7 +5328,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5345,11 +5357,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>50.05757522583008</v>
+        <v>50.05756759643555</v>
       </c>
       <c r="C189" t="n">
         <v>57.9900016784668</v>
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>47.31889343261719</v>
+        <v>47.31888580322266</v>
       </c>
       <c r="C190" t="n">
         <v>54.29999923706055</v>
@@ -5403,11 +5415,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>47.05745697021484</v>
+        <v>47.05744934082031</v>
       </c>
       <c r="C191" t="n">
         <v>54</v>
@@ -5432,11 +5444,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>47.85916900634766</v>
+        <v>47.85917282104492</v>
       </c>
       <c r="C192" t="n">
         <v>54.91999816894531</v>
@@ -5461,11 +5473,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>54.57868957519531</v>
+        <v>54.57868576049805</v>
       </c>
       <c r="C193" t="n">
         <v>62.02000045776367</v>
@@ -5490,11 +5502,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>53.83067321777344</v>
+        <v>53.83068084716797</v>
       </c>
       <c r="C194" t="n">
         <v>61.16999816894531</v>
@@ -5519,11 +5531,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>58.25715637207031</v>
+        <v>58.25717163085938</v>
       </c>
       <c r="C195" t="n">
         <v>66.19999694824219</v>
@@ -5548,7 +5560,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5577,11 +5589,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>64.56683349609375</v>
+        <v>64.56684112548828</v>
       </c>
       <c r="C197" t="n">
         <v>72.84999847412109</v>
@@ -5606,11 +5618,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>60.13534545898438</v>
+        <v>60.13534927368164</v>
       </c>
       <c r="C198" t="n">
         <v>67.84999847412109</v>
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>53.31763076782227</v>
+        <v>53.31763458251953</v>
       </c>
       <c r="C199" t="n">
         <v>59.66999816894531</v>
@@ -5664,11 +5676,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>40.45956420898438</v>
+        <v>40.45955657958984</v>
       </c>
       <c r="C200" t="n">
         <v>45.27999877929688</v>
@@ -5693,11 +5705,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>36.95689010620117</v>
+        <v>36.95688247680664</v>
       </c>
       <c r="C201" t="n">
         <v>41.36000061035156</v>
@@ -5722,11 +5734,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>38.05738067626953</v>
+        <v>38.05738830566406</v>
       </c>
       <c r="C202" t="n">
         <v>42.02999877929688</v>
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>38.31997680664062</v>
+        <v>38.31998825073242</v>
       </c>
       <c r="C203" t="n">
         <v>42.31999969482422</v>
@@ -5780,11 +5792,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>42.98320770263672</v>
+        <v>42.98321151733398</v>
       </c>
       <c r="C204" t="n">
         <v>47.47000122070312</v>
@@ -5809,11 +5821,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>43.24348068237305</v>
+        <v>43.24348831176758</v>
       </c>
       <c r="C205" t="n">
         <v>47.20000076293945</v>
@@ -5838,7 +5850,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5867,11 +5879,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>39.95441436767578</v>
+        <v>39.95441055297852</v>
       </c>
       <c r="C207" t="n">
         <v>43.61000061035156</v>
@@ -5894,11 +5906,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>45.3376350402832</v>
+        <v>45.33762359619141</v>
       </c>
       <c r="C208" t="n">
         <v>49.02000045776367</v>
@@ -5921,11 +5933,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>43.83932876586914</v>
+        <v>43.83931732177734</v>
       </c>
       <c r="C209" t="n">
         <v>47.40000152587891</v>
@@ -5948,11 +5960,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>37.87893295288086</v>
+        <v>37.87892913818359</v>
       </c>
       <c r="C210" t="n">
         <v>40.54999923706055</v>
@@ -5975,11 +5987,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>39.84994125366211</v>
+        <v>39.84994506835938</v>
       </c>
       <c r="C211" t="n">
         <v>42.65999984741211</v>
@@ -6002,7 +6014,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6029,11 +6041,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>36.82335662841797</v>
+        <v>36.8233642578125</v>
       </c>
       <c r="C213" t="n">
         <v>39.41999816894531</v>
@@ -6056,11 +6068,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>34.8752326965332</v>
+        <v>34.875244140625</v>
       </c>
       <c r="C214" t="n">
         <v>36.95000076293945</v>
@@ -6083,7 +6095,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6110,11 +6122,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>38.31103515625</v>
+        <v>38.31103134155273</v>
       </c>
       <c r="C216" t="n">
         <v>40.18999862670898</v>
@@ -6137,11 +6149,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>39.45494079589844</v>
+        <v>39.45493316650391</v>
       </c>
       <c r="C217" t="n">
         <v>41.38999938964844</v>
@@ -6164,11 +6176,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>32.89658355712891</v>
+        <v>32.89658737182617</v>
       </c>
       <c r="C218" t="n">
         <v>34.5099983215332</v>
@@ -6191,11 +6203,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>29.78899765014648</v>
+        <v>29.78899574279785</v>
       </c>
       <c r="C219" t="n">
         <v>31.25</v>
@@ -6218,11 +6230,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>34.43392181396484</v>
+        <v>34.43391799926758</v>
       </c>
       <c r="C220" t="n">
         <v>35.84000015258789</v>
@@ -6245,11 +6257,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>39.04560852050781</v>
+        <v>39.04561233520508</v>
       </c>
       <c r="C221" t="n">
         <v>40.63999938964844</v>
@@ -6272,11 +6284,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>40.29461288452148</v>
+        <v>40.29460525512695</v>
       </c>
       <c r="C222" t="n">
         <v>41.93999862670898</v>
@@ -6299,7 +6311,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6326,11 +6338,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>47.42794036865234</v>
+        <v>47.42794418334961</v>
       </c>
       <c r="C224" t="n">
         <v>49.06999969482422</v>
@@ -6353,11 +6365,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>51.60337829589844</v>
+        <v>51.60337448120117</v>
       </c>
       <c r="C225" t="n">
         <v>53.38999938964844</v>
@@ -6380,11 +6392,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>51.91283416748047</v>
+        <v>51.91283798217773</v>
       </c>
       <c r="C226" t="n">
         <v>53.45000076293945</v>
@@ -6407,11 +6419,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>44.13319778442383</v>
+        <v>44.13319396972656</v>
       </c>
       <c r="C227" t="n">
         <v>45.43999862670898</v>
@@ -6434,11 +6446,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>40.9763069152832</v>
+        <v>40.97631072998047</v>
       </c>
       <c r="C228" t="n">
         <v>41.93999862670898</v>
@@ -6461,11 +6473,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>36.36476898193359</v>
+        <v>36.36477279663086</v>
       </c>
       <c r="C229" t="n">
         <v>37.22000122070312</v>
@@ -6488,11 +6500,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>41.73838806152344</v>
+        <v>41.7383918762207</v>
       </c>
       <c r="C230" t="n">
         <v>42.72000122070312</v>
@@ -6515,11 +6527,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>41.85563659667969</v>
+        <v>41.85563278198242</v>
       </c>
       <c r="C231" t="n">
         <v>42.84000015258789</v>
@@ -6544,11 +6556,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>47.45067596435547</v>
+        <v>47.4506721496582</v>
       </c>
       <c r="C232" t="n">
         <v>48.27999877929688</v>
@@ -6573,7 +6585,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6602,11 +6614,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>52.05698776245117</v>
+        <v>52.05698394775391</v>
       </c>
       <c r="C234" t="n">
         <v>52.72000122070312</v>
@@ -6631,7 +6643,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6660,11 +6672,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>61.31902313232422</v>
+        <v>61.31901931762695</v>
       </c>
       <c r="C236" t="n">
         <v>62.09999847412109</v>
@@ -6689,11 +6701,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>73.46433258056641</v>
+        <v>73.46434020996094</v>
       </c>
       <c r="C237" t="n">
         <v>74.40000152587891</v>
@@ -6718,7 +6730,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6747,11 +6759,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>80.21761322021484</v>
+        <v>80.21762084960938</v>
       </c>
       <c r="C239" t="n">
         <v>80.97000122070312</v>
@@ -6776,7 +6788,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6805,7 +6817,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6834,7 +6846,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6863,7 +6875,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6892,11 +6904,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>107.7734832763672</v>
+        <v>107.7734756469727</v>
       </c>
       <c r="C244" t="n">
         <v>108.25</v>
@@ -6921,7 +6933,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6950,7 +6962,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6979,7 +6991,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7008,7 +7020,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7037,7 +7049,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7066,32 +7078,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>123.5500030517578</v>
+        <v>121.3000030517578</v>
       </c>
       <c r="C250" t="n">
-        <v>123.5500030517578</v>
+        <v>121.3000030517578</v>
       </c>
       <c r="D250" t="n">
-        <v>118749600</v>
+        <v>123858000</v>
       </c>
       <c r="E250" t="n">
         <v>7.92</v>
       </c>
       <c r="F250" t="n">
-        <v>15.59974786007043</v>
+        <v>15.31565695097952</v>
       </c>
       <c r="G250" t="n">
         <v>1053692271</v>
       </c>
       <c r="H250" t="n">
-        <v>130183683297.6636</v>
+        <v>127812875687.9136</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1126985584579656</v>
+        <v>0.117546653239141</v>
       </c>
     </row>
   </sheetData>
@@ -7123,75 +7135,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39448</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7227,13 +7239,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7269,13 +7281,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7311,13 +7323,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7344,7 +7356,7 @@
       <c r="I5" t="n">
         <v>1.83</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K5" t="n">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7390,7 +7402,7 @@
       <c r="I6" t="n">
         <v>1.43</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K6" t="n">
@@ -7403,13 +7415,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7436,7 +7448,7 @@
       <c r="I7" t="n">
         <v>1.17</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K7" t="n">
@@ -7449,13 +7461,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7482,7 +7494,7 @@
       <c r="I8" t="n">
         <v>1.54</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K8" t="n">
@@ -7495,13 +7507,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7528,7 +7540,7 @@
       <c r="I9" t="n">
         <v>2.65</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K9" t="n">
@@ -7541,13 +7553,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40177</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7574,7 +7586,7 @@
       <c r="I10" t="n">
         <v>3.36</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K10" t="n">
@@ -7587,13 +7599,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7620,7 +7632,7 @@
       <c r="I11" t="n">
         <v>3.8</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K11" t="n">
@@ -7633,13 +7645,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7666,7 +7678,7 @@
       <c r="I12" t="n">
         <v>4.08</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K12" t="n">
@@ -7679,13 +7691,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7712,7 +7724,7 @@
       <c r="I13" t="n">
         <v>4.56</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K13" t="n">
@@ -7725,13 +7737,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7758,7 +7770,7 @@
       <c r="I14" t="n">
         <v>4.48</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="K14" t="n">
@@ -7771,13 +7783,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7804,7 +7816,7 @@
       <c r="I15" t="n">
         <v>4.48</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="K15" t="n">
@@ -7817,13 +7829,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7850,7 +7862,7 @@
       <c r="I16" t="n">
         <v>4.390000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="K16" t="n">
@@ -7863,13 +7875,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7896,7 +7908,7 @@
       <c r="I17" t="n">
         <v>0.7599999999999998</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K17" t="n">
@@ -7909,13 +7921,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7942,7 +7954,7 @@
       <c r="I18" t="n">
         <v>0.7</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K18" t="n">
@@ -7955,13 +7967,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7988,7 +8000,7 @@
       <c r="I19" t="n">
         <v>0.49</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="K19" t="n">
@@ -8001,13 +8013,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8034,7 +8046,7 @@
       <c r="I20" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="K20" t="n">
@@ -8047,13 +8059,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8080,7 +8092,7 @@
       <c r="I21" t="n">
         <v>3.63</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K21" t="n">
@@ -8093,13 +8105,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8126,7 +8138,7 @@
       <c r="I22" t="n">
         <v>3.29</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="K22" t="n">
@@ -8139,13 +8151,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8172,7 +8184,7 @@
       <c r="I23" t="n">
         <v>-1.329999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="K23" t="n">
@@ -8185,13 +8197,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8218,7 +8230,7 @@
       <c r="I24" t="n">
         <v>-1.25</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="K24" t="n">
@@ -8231,13 +8243,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8264,7 +8276,7 @@
       <c r="I25" t="n">
         <v>-4.94</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K25" t="n">
@@ -8277,13 +8289,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8310,7 +8322,7 @@
       <c r="I26" t="n">
         <v>-5.369999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K26" t="n">
@@ -8323,13 +8335,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8356,7 +8368,7 @@
       <c r="I27" t="n">
         <v>-0.9499999999999997</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="K27" t="n">
@@ -8369,13 +8381,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8402,7 +8414,7 @@
       <c r="I28" t="n">
         <v>-1.34</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K28" t="n">
@@ -8415,13 +8427,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8448,7 +8460,7 @@
       <c r="I29" t="n">
         <v>1.02</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K29" t="n">
@@ -8461,13 +8473,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8494,7 +8506,7 @@
       <c r="I30" t="n">
         <v>1.19</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="K30" t="n">
@@ -8507,13 +8519,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8540,7 +8552,7 @@
       <c r="I31" t="n">
         <v>0.9700000000000004</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="K31" t="n">
@@ -8553,13 +8565,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8586,7 +8598,7 @@
       <c r="I32" t="n">
         <v>0.9600000000000004</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="K32" t="n">
@@ -8599,13 +8611,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8632,7 +8644,7 @@
       <c r="I33" t="n">
         <v>0.4300000000000004</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="K33" t="n">
@@ -8645,13 +8657,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42480</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8678,7 +8690,7 @@
       <c r="I34" t="n">
         <v>0.1600000000000004</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42480</v>
       </c>
       <c r="K34" t="n">
@@ -8691,13 +8703,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8724,7 +8736,7 @@
       <c r="I35" t="n">
         <v>0.06000000000000043</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="K35" t="n">
@@ -8737,13 +8749,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8770,7 +8782,7 @@
       <c r="I36" t="n">
         <v>-1.03</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K36" t="n">
@@ -8783,13 +8795,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8816,7 +8828,7 @@
       <c r="I37" t="n">
         <v>-1.18</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="K37" t="n">
@@ -8829,13 +8841,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8862,7 +8874,7 @@
       <c r="I38" t="n">
         <v>-1.19</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="K38" t="n">
@@ -8875,13 +8887,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8908,7 +8920,7 @@
       <c r="I39" t="n">
         <v>-0.8999999999999995</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="K39" t="n">
@@ -8921,13 +8933,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8954,7 +8966,7 @@
       <c r="I40" t="n">
         <v>0.1500000000000005</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K40" t="n">
@@ -8967,13 +8979,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9000,7 +9012,7 @@
       <c r="I41" t="n">
         <v>-0.1799999999999995</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K41" t="n">
@@ -9013,13 +9025,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9046,7 +9058,7 @@
       <c r="I42" t="n">
         <v>0.09000000000000052</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K42" t="n">
@@ -9059,13 +9071,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9092,7 +9104,7 @@
       <c r="I43" t="n">
         <v>0.3000000000000005</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K43" t="n">
@@ -9105,13 +9117,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9138,7 +9150,7 @@
       <c r="I44" t="n">
         <v>-0.3499999999999995</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K44" t="n">
@@ -9151,13 +9163,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9184,7 +9196,7 @@
       <c r="I45" t="n">
         <v>0.6400000000000005</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K45" t="n">
@@ -9197,13 +9209,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9230,7 +9242,7 @@
       <c r="I46" t="n">
         <v>0.4400000000000005</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="K46" t="n">
@@ -9243,13 +9255,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9276,7 +9288,7 @@
       <c r="I47" t="n">
         <v>-0.1299999999999996</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K47" t="n">
@@ -9289,13 +9301,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9322,7 +9334,7 @@
       <c r="I48" t="n">
         <v>2.79</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K48" t="n">
@@ -9335,13 +9347,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9368,7 +9380,7 @@
       <c r="I49" t="n">
         <v>3.47</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K49" t="n">
@@ -9381,13 +9393,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9414,7 +9426,7 @@
       <c r="I50" t="n">
         <v>4.33</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K50" t="n">
@@ -9427,13 +9439,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9460,7 +9472,7 @@
       <c r="I51" t="n">
         <v>4.790000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K51" t="n">
@@ -9473,13 +9485,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9506,7 +9518,7 @@
       <c r="I52" t="n">
         <v>3.180000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K52" t="n">
@@ -9519,13 +9531,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9552,7 +9564,7 @@
       <c r="I53" t="n">
         <v>3.51</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="K53" t="n">
@@ -9565,13 +9577,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9598,7 +9610,7 @@
       <c r="I54" t="n">
         <v>3.19</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K54" t="n">
@@ -9611,13 +9623,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9644,7 +9656,7 @@
       <c r="I55" t="n">
         <v>3.57</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="K55" t="n">
@@ -9657,13 +9669,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9690,7 +9702,7 @@
       <c r="I56" t="n">
         <v>2.53</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K56" t="n">
@@ -9703,13 +9715,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9736,7 +9748,7 @@
       <c r="I57" t="n">
         <v>1.46</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K57" t="n">
@@ -9749,13 +9761,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9782,7 +9794,7 @@
       <c r="I58" t="n">
         <v>1.320000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="K58" t="n">
@@ -9795,13 +9807,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9828,7 +9840,7 @@
       <c r="I59" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="K59" t="n">
@@ -9841,13 +9853,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9874,7 +9886,7 @@
       <c r="I60" t="n">
         <v>1.27</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K60" t="n">
@@ -9887,13 +9899,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9920,7 +9932,7 @@
       <c r="I61" t="n">
         <v>-0.5399999999999996</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K61" t="n">
@@ -9933,13 +9945,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9966,7 +9978,7 @@
       <c r="I62" t="n">
         <v>-0.6599999999999997</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K62" t="n">
@@ -9979,13 +9991,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10012,7 +10024,7 @@
       <c r="I63" t="n">
         <v>-0.9599999999999996</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="K63" t="n">
@@ -10025,13 +10037,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10058,7 +10070,7 @@
       <c r="I64" t="n">
         <v>-1.03</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K64" t="n">
@@ -10071,13 +10083,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10104,7 +10116,7 @@
       <c r="I65" t="n">
         <v>-2.97</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="K65" t="n">
@@ -10117,13 +10129,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10150,7 +10162,7 @@
       <c r="I66" t="n">
         <v>-3.26</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="K66" t="n">
@@ -10163,13 +10175,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10196,7 +10208,7 @@
       <c r="I67" t="n">
         <v>-2.71</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K67" t="n">
@@ -10209,13 +10221,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10242,7 +10254,7 @@
       <c r="I68" t="n">
         <v>-2.11</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="K68" t="n">
@@ -10255,13 +10267,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10288,7 +10300,7 @@
       <c r="I69" t="n">
         <v>2.92</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K69" t="n">
@@ -10301,13 +10313,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10334,7 +10346,7 @@
       <c r="I70" t="n">
         <v>4.45</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K70" t="n">
@@ -10347,13 +10359,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10380,7 +10392,7 @@
       <c r="I71" t="n">
         <v>5.56</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K71" t="n">
@@ -10393,13 +10405,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10426,7 +10438,7 @@
       <c r="I72" t="n">
         <v>6.43</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="K72" t="n">
@@ -10439,13 +10451,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10472,7 +10484,7 @@
       <c r="I73" t="n">
         <v>6.389999999999999</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K73" t="n">
@@ -10485,13 +10497,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10518,7 +10530,7 @@
       <c r="I74" t="n">
         <v>7.709999999999999</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K74" t="n">
@@ -10531,13 +10543,13 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -10564,7 +10576,7 @@
       <c r="I75" t="n">
         <v>7.92</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K75" t="n">
@@ -10601,52 +10613,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39925</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="C2" t="n">
@@ -10675,10 +10687,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40009</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="C3" t="n">
@@ -10707,10 +10719,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40109</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="C4" t="n">
@@ -10739,10 +10751,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40226</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C5" t="n">
@@ -10771,10 +10783,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40288</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40295</v>
       </c>
       <c r="C6" t="n">
@@ -10803,10 +10815,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40379</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="C7" t="n">
@@ -10835,10 +10847,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="C8" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40645</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="C9" t="n">
@@ -10899,10 +10911,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40745</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="C10" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40836</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C11" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10995,10 +11007,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41017</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C13" t="n">
@@ -11027,10 +11039,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41108</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="C14" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41207</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C15" t="n">
@@ -11091,10 +11103,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C16" t="n">
@@ -11123,10 +11135,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41386</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="C17" t="n">
@@ -11155,10 +11167,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41473</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="C18" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41571</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="C19" t="n">
@@ -11219,10 +11231,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41683</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C20" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41745</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C21" t="n">
@@ -11283,10 +11295,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="C22" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41934</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C23" t="n">
@@ -11347,10 +11359,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42046</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C24" t="n">
@@ -11379,10 +11391,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42109</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="C25" t="n">
@@ -11411,10 +11423,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42201</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="C26" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42299</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="C27" t="n">
@@ -11475,10 +11487,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42409</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="C28" t="n">
@@ -11507,10 +11519,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42473</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42480</v>
       </c>
       <c r="C29" t="n">
@@ -11539,10 +11551,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42564</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="C30" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42662</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C31" t="n">
@@ -11603,10 +11615,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42780</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="C32" t="n">
@@ -11635,10 +11647,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42842</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="C33" t="n">
@@ -11667,10 +11679,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42933</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="C34" t="n">
@@ -11699,10 +11711,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43027</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C35" t="n">
@@ -11731,10 +11743,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43146</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C36" t="n">
@@ -11763,10 +11775,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43209</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C37" t="n">
@@ -11795,10 +11807,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43300</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C38" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43391</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C39" t="n">
@@ -11859,10 +11871,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43510</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C40" t="n">
@@ -11891,10 +11903,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43573</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C41" t="n">
@@ -11923,10 +11935,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43664</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C42" t="n">
@@ -11955,10 +11967,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43767</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C43" t="n">
@@ -11987,10 +11999,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43874</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C44" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43949</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -12051,10 +12063,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44035</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C46" t="n">
@@ -12083,10 +12095,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44126</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C47" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44238</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="C48" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C49" t="n">
@@ -12179,10 +12191,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44392</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="C50" t="n">
@@ -12211,10 +12223,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44490</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C51" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44609</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C52" t="n">
@@ -12275,10 +12287,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44669</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="C53" t="n">
@@ -12307,10 +12319,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44760</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="C54" t="n">
@@ -12339,10 +12351,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44859</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C55" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C56" t="n">
@@ -12403,10 +12415,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45036</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C57" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45120</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="C58" t="n">
@@ -12467,10 +12479,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45218</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C59" t="n">
@@ -12499,10 +12511,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="C60" t="n">
@@ -12531,10 +12543,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45404</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="C61" t="n">
@@ -12563,10 +12575,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45491</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C62" t="n">
@@ -12595,10 +12607,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45582</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="C63" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45701</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C64" t="n">
@@ -12659,10 +12671,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45763</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C65" t="n">
@@ -12691,10 +12703,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C66" t="n">
@@ -12723,10 +12735,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45946</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="C67" t="n">
@@ -12755,10 +12767,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46065</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C68" t="n">
@@ -12787,10 +12799,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46128</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C69" t="n">
@@ -12819,10 +12831,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C70" t="n">
@@ -12869,12 +12881,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/NEM.xlsx
+++ b/salidas/empresas/NEM.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.86658096313477</v>
+        <v>41.8665771484375</v>
       </c>
       <c r="C2" t="n">
         <v>61.79999923706055</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>35.85078048706055</v>
+        <v>35.85078430175781</v>
       </c>
       <c r="C3" t="n">
         <v>52.91999816894531</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>39.61048889160156</v>
+        <v>39.61050033569336</v>
       </c>
       <c r="C5" t="n">
         <v>58.36000061035156</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>35.39561462402344</v>
+        <v>35.39560317993164</v>
       </c>
       <c r="C6" t="n">
         <v>52.15000152587891</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>35.99347305297852</v>
+        <v>35.99348068237305</v>
       </c>
       <c r="C7" t="n">
         <v>52.93000030517578</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.83744812011719</v>
+        <v>34.83743667602539</v>
       </c>
       <c r="C8" t="n">
         <v>51.22999954223633</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>34.85104370117188</v>
+        <v>34.85103225708008</v>
       </c>
       <c r="C9" t="n">
         <v>51.25</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>29.12776565551758</v>
+        <v>29.12774085998535</v>
       </c>
       <c r="C10" t="n">
         <v>42.75</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>30.84475517272949</v>
+        <v>30.84475326538086</v>
       </c>
       <c r="C11" t="n">
         <v>45.27000045776367</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>30.82818412780762</v>
+        <v>30.82817077636719</v>
       </c>
       <c r="C13" t="n">
         <v>45.15000152587891</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>28.73718452453613</v>
+        <v>28.7371940612793</v>
       </c>
       <c r="C16" t="n">
         <v>41.9900016784668</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>28.53873825073242</v>
+        <v>28.53872489929199</v>
       </c>
       <c r="C17" t="n">
         <v>41.70000076293945</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>27.84064102172852</v>
+        <v>27.84065055847168</v>
       </c>
       <c r="C18" t="n">
         <v>40.68000030517578</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>26.796630859375</v>
+        <v>26.79663276672363</v>
       </c>
       <c r="C19" t="n">
         <v>39.06000137329102</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>28.64208602905273</v>
+        <v>28.64206886291504</v>
       </c>
       <c r="C20" t="n">
         <v>41.75</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>28.99193572998047</v>
+        <v>28.99195861816406</v>
       </c>
       <c r="C21" t="n">
         <v>42.2599983215332</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>30.75923156738281</v>
+        <v>30.75925827026367</v>
       </c>
       <c r="C22" t="n">
         <v>44.72999954223633</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>35.00214767456055</v>
+        <v>35.00214385986328</v>
       </c>
       <c r="C23" t="n">
         <v>50.90000152587891</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>34.17006683349609</v>
+        <v>34.17004776000977</v>
       </c>
       <c r="C24" t="n">
         <v>49.68999862670898</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>33.64642715454102</v>
+        <v>33.64644622802734</v>
       </c>
       <c r="C25" t="n">
         <v>48.83000183105469</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>37.38111114501953</v>
+        <v>37.38109588623047</v>
       </c>
       <c r="C26" t="n">
         <v>54.25</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>35.25881576538086</v>
+        <v>35.25882339477539</v>
       </c>
       <c r="C27" t="n">
         <v>51.16999816894531</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.27639961242676</v>
+        <v>31.27639198303223</v>
       </c>
       <c r="C28" t="n">
         <v>45.29999923706055</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>30.52383804321289</v>
+        <v>30.52382469177246</v>
       </c>
       <c r="C29" t="n">
         <v>44.20999908447266</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>36.08950424194336</v>
+        <v>36.08951568603516</v>
       </c>
       <c r="C31" t="n">
         <v>52.15999984741211</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>33.18352890014648</v>
+        <v>33.18351745605469</v>
       </c>
       <c r="C32" t="n">
         <v>47.95999908447266</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>31.20468521118164</v>
+        <v>31.20469093322754</v>
       </c>
       <c r="C33" t="n">
         <v>45.09999847412109</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>26.88067054748535</v>
+        <v>26.88067626953125</v>
       </c>
       <c r="C34" t="n">
         <v>38.7599983215332</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>18.2672061920166</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="C35" t="n">
         <v>26.34000015258789</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>23.33680725097656</v>
+        <v>23.33680534362793</v>
       </c>
       <c r="C36" t="n">
         <v>33.65000152587891</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>28.31386184692383</v>
+        <v>28.31384658813477</v>
       </c>
       <c r="C37" t="n">
         <v>40.70000076293945</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>27.6738224029541</v>
+        <v>27.67383575439453</v>
       </c>
       <c r="C38" t="n">
         <v>39.77999877929688</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.9608211517334</v>
+        <v>28.96082878112793</v>
       </c>
       <c r="C39" t="n">
         <v>41.63000106811523</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>31.21894454956055</v>
+        <v>31.21894836425781</v>
       </c>
       <c r="C40" t="n">
         <v>44.7599983215332</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>28.06636238098145</v>
+        <v>28.06636428833008</v>
       </c>
       <c r="C41" t="n">
         <v>40.2400016784668</v>
@@ -1264,7 +1264,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>34.08556365966797</v>
+        <v>34.0855712890625</v>
       </c>
       <c r="C42" t="n">
         <v>48.86999893188477</v>
@@ -1289,7 +1289,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>28.56464004516602</v>
+        <v>28.56465911865234</v>
       </c>
       <c r="C43" t="n">
         <v>40.86999893188477</v>
@@ -1314,7 +1314,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>28.90011405944824</v>
+        <v>28.90011596679688</v>
       </c>
       <c r="C44" t="n">
         <v>41.34999847412109</v>
@@ -1339,7 +1339,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>28.08938980102539</v>
+        <v>28.08938598632812</v>
       </c>
       <c r="C45" t="n">
         <v>40.18999862670898</v>
@@ -1364,7 +1364,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>30.83647155761719</v>
+        <v>30.83646965026855</v>
       </c>
       <c r="C46" t="n">
         <v>44.02000045776367</v>
@@ -1389,7 +1389,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>30.44417190551758</v>
+        <v>30.44418907165527</v>
       </c>
       <c r="C47" t="n">
         <v>43.45999908447266</v>
@@ -1414,7 +1414,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>37.57538223266602</v>
+        <v>37.57536697387695</v>
       </c>
       <c r="C48" t="n">
         <v>53.63999938964844</v>
@@ -1439,7 +1439,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.20198059082031</v>
+        <v>33.20197677612305</v>
       </c>
       <c r="C49" t="n">
         <v>47.31000137329102</v>
@@ -1489,7 +1489,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>34.58451843261719</v>
+        <v>34.58452224731445</v>
       </c>
       <c r="C51" t="n">
         <v>49.27999877929688</v>
@@ -1514,7 +1514,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>35.81247711181641</v>
+        <v>35.81248092651367</v>
       </c>
       <c r="C52" t="n">
         <v>50.93000030517578</v>
@@ -1539,7 +1539,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>39.43379974365234</v>
+        <v>39.43379211425781</v>
       </c>
       <c r="C53" t="n">
         <v>56.08000183105469</v>
@@ -1564,7 +1564,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>37.84463119506836</v>
+        <v>37.84464263916016</v>
       </c>
       <c r="C54" t="n">
         <v>53.81999969482422</v>
@@ -1589,7 +1589,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>43.49126052856445</v>
+        <v>43.49126815795898</v>
       </c>
       <c r="C55" t="n">
         <v>61.7400016784668</v>
@@ -1614,7 +1614,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.37741088867188</v>
+        <v>39.37742233276367</v>
       </c>
       <c r="C56" t="n">
         <v>55.90000152587891</v>
@@ -1639,7 +1639,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>43.19538116455078</v>
+        <v>43.19540405273438</v>
       </c>
       <c r="C57" t="n">
         <v>61.31999969482422</v>
@@ -1664,7 +1664,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>44.35311508178711</v>
+        <v>44.35312652587891</v>
       </c>
       <c r="C58" t="n">
         <v>62.81000137329102</v>
@@ -1689,7 +1689,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>42.97613525390625</v>
+        <v>42.97613143920898</v>
       </c>
       <c r="C59" t="n">
         <v>60.86000061035156</v>
@@ -1714,7 +1714,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>41.54266357421875</v>
+        <v>41.54264068603516</v>
       </c>
       <c r="C60" t="n">
         <v>58.83000183105469</v>
@@ -1739,7 +1739,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>43.48324584960938</v>
+        <v>43.48323440551758</v>
       </c>
       <c r="C61" t="n">
         <v>61.43000030517578</v>
@@ -1764,7 +1764,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>38.98130416870117</v>
+        <v>38.98129272460938</v>
       </c>
       <c r="C62" t="n">
         <v>55.06999969482422</v>
@@ -1789,7 +1789,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>39.12285995483398</v>
+        <v>39.12287139892578</v>
       </c>
       <c r="C63" t="n">
         <v>55.27000045776367</v>
@@ -1818,7 +1818,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>38.74733734130859</v>
+        <v>38.74732208251953</v>
       </c>
       <c r="C64" t="n">
         <v>54.58000183105469</v>
@@ -1847,7 +1847,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>41.60830688476562</v>
+        <v>41.60830307006836</v>
       </c>
       <c r="C65" t="n">
         <v>58.61000061035156</v>
@@ -1876,7 +1876,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>40.16007232666016</v>
+        <v>40.16005325317383</v>
       </c>
       <c r="C66" t="n">
         <v>56.56999969482422</v>
@@ -1905,7 +1905,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>38.46249389648438</v>
+        <v>38.46250534057617</v>
       </c>
       <c r="C67" t="n">
         <v>53.97000122070312</v>
@@ -1934,7 +1934,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>39.63126754760742</v>
+        <v>39.63128662109375</v>
       </c>
       <c r="C68" t="n">
         <v>55.61000061035156</v>
@@ -1992,7 +1992,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>45.07196044921875</v>
+        <v>45.07195281982422</v>
       </c>
       <c r="C70" t="n">
         <v>62.95000076293945</v>
@@ -2021,7 +2021,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>47.85004425048828</v>
+        <v>47.85002136230469</v>
       </c>
       <c r="C71" t="n">
         <v>66.83000183105469</v>
@@ -2050,7 +2050,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>49.31781768798828</v>
+        <v>49.31782150268555</v>
       </c>
       <c r="C72" t="n">
         <v>68.87999725341797</v>
@@ -2079,7 +2079,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.19482421875</v>
+        <v>43.19481658935547</v>
       </c>
       <c r="C73" t="n">
         <v>60.0099983215332</v>
@@ -2108,7 +2108,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>44.25291442871094</v>
+        <v>44.2529296875</v>
       </c>
       <c r="C74" t="n">
         <v>61.47999954223633</v>
@@ -2137,7 +2137,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>42.77733993530273</v>
+        <v>42.7773323059082</v>
       </c>
       <c r="C75" t="n">
         <v>59.43000030517578</v>
@@ -2166,7 +2166,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>37.1369743347168</v>
+        <v>37.13697814941406</v>
       </c>
       <c r="C76" t="n">
         <v>51.27000045776367</v>
@@ -2195,7 +2195,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>34.51486206054688</v>
+        <v>34.51486587524414</v>
       </c>
       <c r="C77" t="n">
         <v>47.65000152587891</v>
@@ -2224,7 +2224,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>34.15991973876953</v>
+        <v>34.15994644165039</v>
       </c>
       <c r="C78" t="n">
         <v>47.15999984741211</v>
@@ -2253,7 +2253,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>35.38208770751953</v>
+        <v>35.38209915161133</v>
       </c>
       <c r="C79" t="n">
         <v>48.5099983215332</v>
@@ -2282,7 +2282,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>32.43542098999023</v>
+        <v>32.43540573120117</v>
       </c>
       <c r="C80" t="n">
         <v>44.47000122070312</v>
@@ -2311,7 +2311,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>36.96484375</v>
+        <v>36.96485137939453</v>
       </c>
       <c r="C81" t="n">
         <v>50.68000030517578</v>
@@ -2340,7 +2340,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>41.14385604858398</v>
+        <v>41.14384841918945</v>
       </c>
       <c r="C82" t="n">
         <v>56.02000045776367</v>
@@ -2369,7 +2369,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>40.08625030517578</v>
+        <v>40.08627319335938</v>
       </c>
       <c r="C83" t="n">
         <v>54.58000183105469</v>
@@ -2398,7 +2398,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>34.58522415161133</v>
+        <v>34.58522796630859</v>
       </c>
       <c r="C84" t="n">
         <v>47.09000015258789</v>
@@ -2427,7 +2427,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>34.37118530273438</v>
+        <v>34.37119674682617</v>
       </c>
       <c r="C85" t="n">
         <v>46.43999862670898</v>
@@ -2456,7 +2456,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>31.79555702209473</v>
+        <v>31.79556846618652</v>
       </c>
       <c r="C86" t="n">
         <v>42.95999908447266</v>
@@ -2485,7 +2485,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>29.8194522857666</v>
+        <v>29.81944847106934</v>
       </c>
       <c r="C87" t="n">
         <v>40.29000091552734</v>
@@ -2514,7 +2514,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>31.3430347442627</v>
+        <v>31.34301948547363</v>
       </c>
       <c r="C88" t="n">
         <v>41.88999938964844</v>
@@ -2543,7 +2543,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>24.24239921569824</v>
+        <v>24.24239730834961</v>
       </c>
       <c r="C89" t="n">
         <v>32.40000152587891</v>
@@ -2572,7 +2572,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.64905548095703</v>
+        <v>25.64905738830566</v>
       </c>
       <c r="C90" t="n">
         <v>34.27999877929688</v>
@@ -2601,7 +2601,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>22.64158058166504</v>
+        <v>22.64157485961914</v>
       </c>
       <c r="C91" t="n">
         <v>29.95000076293945</v>
@@ -2630,7 +2630,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>22.67937660217285</v>
+        <v>22.67937469482422</v>
       </c>
       <c r="C92" t="n">
         <v>30</v>
@@ -2684,7 +2684,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>21.41150283813477</v>
+        <v>21.4114990234375</v>
       </c>
       <c r="C94" t="n">
         <v>28.10000038146973</v>
@@ -2711,7 +2711,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>20.77143859863281</v>
+        <v>20.77144241333008</v>
       </c>
       <c r="C95" t="n">
         <v>27.26000022888184</v>
@@ -2738,7 +2738,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>18.91984939575195</v>
+        <v>18.91983413696289</v>
       </c>
       <c r="C96" t="n">
         <v>24.82999992370605</v>
@@ -2765,7 +2765,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>17.69681739807129</v>
+        <v>17.69681358337402</v>
       </c>
       <c r="C97" t="n">
         <v>23.03000068664551</v>
@@ -2792,7 +2792,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>16.59796142578125</v>
+        <v>16.59796524047852</v>
       </c>
       <c r="C98" t="n">
         <v>21.60000038146973</v>
@@ -2819,7 +2819,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>17.87355041503906</v>
+        <v>17.87355422973633</v>
       </c>
       <c r="C99" t="n">
         <v>23.26000022888184</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>19.19844055175781</v>
+        <v>19.19843101501465</v>
       </c>
       <c r="C101" t="n">
         <v>24.82999992370605</v>
@@ -2900,7 +2900,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>17.69843864440918</v>
+        <v>17.69844627380371</v>
       </c>
       <c r="C102" t="n">
         <v>22.88999938964844</v>
@@ -2927,7 +2927,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>19.69180107116699</v>
+        <v>19.69180297851562</v>
       </c>
       <c r="C103" t="n">
         <v>25.44000053405762</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>19.28156280517578</v>
+        <v>19.28155708312988</v>
       </c>
       <c r="C104" t="n">
         <v>24.90999984741211</v>
@@ -3035,7 +3035,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>14.5355224609375</v>
+        <v>14.53552341461182</v>
       </c>
       <c r="C107" t="n">
         <v>18.76000022888184</v>
@@ -3062,7 +3062,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>14.25659275054932</v>
+        <v>14.25658893585205</v>
       </c>
       <c r="C108" t="n">
         <v>18.39999961853027</v>
@@ -3116,7 +3116,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>19.51202201843262</v>
+        <v>19.51202392578125</v>
       </c>
       <c r="C110" t="n">
         <v>25.14999961853027</v>
@@ -3143,7 +3143,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>20.4274959564209</v>
+        <v>20.42749977111816</v>
       </c>
       <c r="C111" t="n">
         <v>26.32999992370605</v>
@@ -3201,7 +3201,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>20.57457160949707</v>
+        <v>20.5745677947998</v>
       </c>
       <c r="C113" t="n">
         <v>26.48999977111816</v>
@@ -3230,7 +3230,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>21.1570930480957</v>
+        <v>21.1570873260498</v>
       </c>
       <c r="C114" t="n">
         <v>27.23999977111816</v>
@@ -3259,7 +3259,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>18.16109848022461</v>
+        <v>18.16110229492188</v>
       </c>
       <c r="C115" t="n">
         <v>23.36000061035156</v>
@@ -3288,7 +3288,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>13.34871482849121</v>
+        <v>13.34871768951416</v>
       </c>
       <c r="C116" t="n">
         <v>17.17000007629395</v>
@@ -3317,7 +3317,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>13.27097320556641</v>
+        <v>13.27097225189209</v>
       </c>
       <c r="C117" t="n">
         <v>17.06999969482422</v>
@@ -3346,7 +3346,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>12.51345348358154</v>
+        <v>12.51345539093018</v>
       </c>
       <c r="C118" t="n">
         <v>16.06999969482422</v>
@@ -3375,7 +3375,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>15.15319442749023</v>
+        <v>15.15320014953613</v>
       </c>
       <c r="C119" t="n">
         <v>19.45999908447266</v>
@@ -3404,7 +3404,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>14.33557796478271</v>
+        <v>14.33557510375977</v>
       </c>
       <c r="C120" t="n">
         <v>18.40999984741211</v>
@@ -3433,7 +3433,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>14.02661991119385</v>
+        <v>14.02662086486816</v>
       </c>
       <c r="C121" t="n">
         <v>17.98999977111816</v>
@@ -3491,7 +3491,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>20.13938903808594</v>
+        <v>20.1393928527832</v>
       </c>
       <c r="C123" t="n">
         <v>25.82999992370605</v>
@@ -3520,7 +3520,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>20.74371337890625</v>
+        <v>20.74370384216309</v>
       </c>
       <c r="C124" t="n">
         <v>26.57999992370605</v>
@@ -3549,7 +3549,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>27.29147148132324</v>
+        <v>27.29147911071777</v>
       </c>
       <c r="C125" t="n">
         <v>34.97000122070312</v>
@@ -3578,7 +3578,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>25.29358100891113</v>
+        <v>25.29358291625977</v>
       </c>
       <c r="C126" t="n">
         <v>32.40999984741211</v>
@@ -3607,7 +3607,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>30.55179977416992</v>
+        <v>30.55178833007812</v>
       </c>
       <c r="C127" t="n">
         <v>39.11999893188477</v>
@@ -3636,7 +3636,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>34.36296844482422</v>
+        <v>34.36295318603516</v>
       </c>
       <c r="C128" t="n">
         <v>44</v>
@@ -3665,7 +3665,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>29.86453056335449</v>
+        <v>29.86453437805176</v>
       </c>
       <c r="C129" t="n">
         <v>38.2400016784668</v>
@@ -3694,7 +3694,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>30.70358085632324</v>
+        <v>30.70356941223145</v>
       </c>
       <c r="C130" t="n">
         <v>39.29000091552734</v>
@@ -3723,7 +3723,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>28.94531440734863</v>
+        <v>28.94529724121094</v>
       </c>
       <c r="C131" t="n">
         <v>37.04000091552734</v>
@@ -3750,7 +3750,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>25.35057640075684</v>
+        <v>25.3505802154541</v>
       </c>
       <c r="C132" t="n">
         <v>32.43999862670898</v>
@@ -3777,7 +3777,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.66418266296387</v>
+        <v>26.66417503356934</v>
       </c>
       <c r="C133" t="n">
         <v>34.06999969482422</v>
@@ -3804,7 +3804,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>28.393798828125</v>
+        <v>28.3937816619873</v>
       </c>
       <c r="C134" t="n">
         <v>36.27999877929688</v>
@@ -3831,7 +3831,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>26.7972297668457</v>
+        <v>26.79723167419434</v>
       </c>
       <c r="C135" t="n">
         <v>34.2400016784668</v>
@@ -3858,7 +3858,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>25.83459091186523</v>
+        <v>25.83459854125977</v>
       </c>
       <c r="C136" t="n">
         <v>32.95999908447266</v>
@@ -3885,7 +3885,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>26.5008373260498</v>
+        <v>26.5008430480957</v>
       </c>
       <c r="C137" t="n">
         <v>33.81000137329102</v>
@@ -3912,7 +3912,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>26.7673397064209</v>
+        <v>26.76733207702637</v>
       </c>
       <c r="C138" t="n">
         <v>34.15000152587891</v>
@@ -3939,7 +3939,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>25.42538070678711</v>
+        <v>25.42538261413574</v>
       </c>
       <c r="C139" t="n">
         <v>32.38999938964844</v>
@@ -3966,7 +3966,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>29.17757415771484</v>
+        <v>29.17757225036621</v>
       </c>
       <c r="C140" t="n">
         <v>37.16999816894531</v>
@@ -3993,7 +3993,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>30.09598731994629</v>
+        <v>30.09599113464355</v>
       </c>
       <c r="C141" t="n">
         <v>38.34000015258789</v>
@@ -4020,7 +4020,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>29.50215721130371</v>
+        <v>29.50216484069824</v>
       </c>
       <c r="C142" t="n">
         <v>37.5099983215332</v>
@@ -4047,7 +4047,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>28.44037246704102</v>
+        <v>28.44037055969238</v>
       </c>
       <c r="C143" t="n">
         <v>36.15999984741211</v>
@@ -4076,7 +4076,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>29.09317398071289</v>
+        <v>29.09317016601562</v>
       </c>
       <c r="C144" t="n">
         <v>36.9900016784668</v>
@@ -4134,7 +4134,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.92853736877441</v>
+        <v>31.92853355407715</v>
       </c>
       <c r="C146" t="n">
         <v>40.5099983215332</v>
@@ -4163,7 +4163,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>30.10788154602051</v>
+        <v>30.10787963867188</v>
       </c>
       <c r="C147" t="n">
         <v>38.20000076293945</v>
@@ -4190,7 +4190,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>30.90494155883789</v>
+        <v>30.90494918823242</v>
       </c>
       <c r="C148" t="n">
         <v>39.06999969482422</v>
@@ -4246,7 +4246,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>30.79421424865723</v>
+        <v>30.79421043395996</v>
       </c>
       <c r="C150" t="n">
         <v>38.93000030517578</v>
@@ -4275,7 +4275,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>29.93790245056152</v>
+        <v>29.93789100646973</v>
       </c>
       <c r="C151" t="n">
         <v>37.70999908447266</v>
@@ -4304,7 +4304,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>29.12017059326172</v>
+        <v>29.12016677856445</v>
       </c>
       <c r="C152" t="n">
         <v>36.68000030517578</v>
@@ -4333,7 +4333,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>24.63465118408203</v>
+        <v>24.6346549987793</v>
       </c>
       <c r="C153" t="n">
         <v>31.03000068664551</v>
@@ -4362,7 +4362,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>24.08953857421875</v>
+        <v>24.08954048156738</v>
       </c>
       <c r="C154" t="n">
         <v>30.20000076293945</v>
@@ -4391,7 +4391,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>24.66386032104492</v>
+        <v>24.66386222839355</v>
       </c>
       <c r="C155" t="n">
         <v>30.92000007629395</v>
@@ -4418,7 +4418,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>25.79654693603516</v>
+        <v>25.79654884338379</v>
       </c>
       <c r="C156" t="n">
         <v>32.34000015258789</v>
@@ -4445,7 +4445,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>27.75414657592773</v>
+        <v>27.754150390625</v>
       </c>
       <c r="C157" t="n">
         <v>34.65000152587891</v>
@@ -4472,7 +4472,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>27.32161521911621</v>
+        <v>27.32161712646484</v>
       </c>
       <c r="C158" t="n">
         <v>34.11000061035156</v>
@@ -4499,7 +4499,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>27.32962799072266</v>
+        <v>27.32963371276855</v>
       </c>
       <c r="C159" t="n">
         <v>34.11999893188477</v>
@@ -4644,7 +4644,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>30.22673988342285</v>
+        <v>30.22673797607422</v>
       </c>
       <c r="C164" t="n">
         <v>36.52000045776367</v>
@@ -4671,7 +4671,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>33.01600646972656</v>
+        <v>33.01601409912109</v>
       </c>
       <c r="C165" t="n">
         <v>39.88999938964844</v>
@@ -4698,7 +4698,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>31.50105667114258</v>
+        <v>31.50105857849121</v>
       </c>
       <c r="C166" t="n">
         <v>37.91999816894531</v>
@@ -4725,7 +4725,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>33.00468063354492</v>
+        <v>33.00466918945312</v>
       </c>
       <c r="C167" t="n">
         <v>39.72999954223633</v>
@@ -4839,7 +4839,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>37.20750427246094</v>
+        <v>37.2075080871582</v>
       </c>
       <c r="C171" t="n">
         <v>44.63000106811523</v>
@@ -4868,7 +4868,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>37.85596466064453</v>
+        <v>37.85597229003906</v>
       </c>
       <c r="C172" t="n">
         <v>45.27999877929688</v>
@@ -4897,7 +4897,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>49.72776031494141</v>
+        <v>49.72776412963867</v>
       </c>
       <c r="C173" t="n">
         <v>59.47999954223633</v>
@@ -4926,7 +4926,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>48.88335037231445</v>
+        <v>48.88335800170898</v>
       </c>
       <c r="C174" t="n">
         <v>58.47000122070312</v>
@@ -4955,7 +4955,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>51.83887481689453</v>
+        <v>51.83885955810547</v>
       </c>
       <c r="C175" t="n">
         <v>61.7400016784668</v>
@@ -4984,7 +4984,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>58.10252380371094</v>
+        <v>58.10251235961914</v>
       </c>
       <c r="C176" t="n">
         <v>69.19999694824219</v>
@@ -5013,7 +5013,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>56.49043273925781</v>
+        <v>56.49042129516602</v>
       </c>
       <c r="C177" t="n">
         <v>67.27999877929688</v>
@@ -5042,7 +5042,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>53.47791290283203</v>
+        <v>53.4779167175293</v>
       </c>
       <c r="C178" t="n">
         <v>63.45000076293945</v>
@@ -5071,7 +5071,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>52.96377563476562</v>
+        <v>52.96378326416016</v>
       </c>
       <c r="C179" t="n">
         <v>62.84000015258789</v>
@@ -5100,7 +5100,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>49.57558059692383</v>
+        <v>49.57557678222656</v>
       </c>
       <c r="C180" t="n">
         <v>58.81999969482422</v>
@@ -5129,7 +5129,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>50.81630706787109</v>
+        <v>50.8162956237793</v>
       </c>
       <c r="C181" t="n">
         <v>59.88999938964844</v>
@@ -5158,7 +5158,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>50.57023239135742</v>
+        <v>50.57024383544922</v>
       </c>
       <c r="C182" t="n">
         <v>59.59999847412109</v>
@@ -5187,7 +5187,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>46.1411018371582</v>
+        <v>46.14109802246094</v>
       </c>
       <c r="C183" t="n">
         <v>54.38000106811523</v>
@@ -5245,7 +5245,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>53.47226715087891</v>
+        <v>53.4722785949707</v>
       </c>
       <c r="C185" t="n">
         <v>62.40999984741211</v>
@@ -5274,7 +5274,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>62.95694732666016</v>
+        <v>62.95695495605469</v>
       </c>
       <c r="C186" t="n">
         <v>73.48000335693359</v>
@@ -5332,7 +5332,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>54.22687149047852</v>
+        <v>54.22688293457031</v>
       </c>
       <c r="C188" t="n">
         <v>62.81999969482422</v>
@@ -5361,7 +5361,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>50.05756759643555</v>
+        <v>50.05756378173828</v>
       </c>
       <c r="C189" t="n">
         <v>57.9900016784668</v>
@@ -5390,7 +5390,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>47.31888580322266</v>
+        <v>47.31888198852539</v>
       </c>
       <c r="C190" t="n">
         <v>54.29999923706055</v>
@@ -5419,7 +5419,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>47.05744934082031</v>
+        <v>47.05745315551758</v>
       </c>
       <c r="C191" t="n">
         <v>54</v>
@@ -5477,7 +5477,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>54.57868576049805</v>
+        <v>54.57868957519531</v>
       </c>
       <c r="C193" t="n">
         <v>62.02000045776367</v>
@@ -5506,7 +5506,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>53.83068084716797</v>
+        <v>53.83067321777344</v>
       </c>
       <c r="C194" t="n">
         <v>61.16999816894531</v>
@@ -5535,7 +5535,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>58.25717163085938</v>
+        <v>58.25715637207031</v>
       </c>
       <c r="C195" t="n">
         <v>66.19999694824219</v>
@@ -5564,7 +5564,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>70.41640472412109</v>
+        <v>70.41641235351562</v>
       </c>
       <c r="C196" t="n">
         <v>79.44999694824219</v>
@@ -5593,7 +5593,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>64.56684112548828</v>
+        <v>64.56683349609375</v>
       </c>
       <c r="C197" t="n">
         <v>72.84999847412109</v>
@@ -5622,7 +5622,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>60.13534927368164</v>
+        <v>60.13535308837891</v>
       </c>
       <c r="C198" t="n">
         <v>67.84999847412109</v>
@@ -5651,7 +5651,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>53.31763458251953</v>
+        <v>53.31763076782227</v>
       </c>
       <c r="C199" t="n">
         <v>59.66999816894531</v>
@@ -5680,7 +5680,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>40.45955657958984</v>
+        <v>40.45956039428711</v>
       </c>
       <c r="C200" t="n">
         <v>45.27999877929688</v>
@@ -5709,7 +5709,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>36.95688247680664</v>
+        <v>36.95687866210938</v>
       </c>
       <c r="C201" t="n">
         <v>41.36000061035156</v>
@@ -5738,7 +5738,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>38.05738830566406</v>
+        <v>38.0573844909668</v>
       </c>
       <c r="C202" t="n">
         <v>42.02999877929688</v>
@@ -5767,7 +5767,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>38.31998825073242</v>
+        <v>38.31998062133789</v>
       </c>
       <c r="C203" t="n">
         <v>42.31999969482422</v>
@@ -5854,7 +5854,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>48.4931640625</v>
+        <v>48.49317169189453</v>
       </c>
       <c r="C206" t="n">
         <v>52.93000030517578</v>
@@ -5883,7 +5883,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>39.95441055297852</v>
+        <v>39.95440673828125</v>
       </c>
       <c r="C207" t="n">
         <v>43.61000061035156</v>
@@ -5937,7 +5937,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>43.83931732177734</v>
+        <v>43.83932113647461</v>
       </c>
       <c r="C209" t="n">
         <v>47.40000152587891</v>
@@ -5964,7 +5964,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>37.87892913818359</v>
+        <v>37.87893676757812</v>
       </c>
       <c r="C210" t="n">
         <v>40.54999923706055</v>
@@ -5991,7 +5991,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>39.84994506835938</v>
+        <v>39.84994125366211</v>
       </c>
       <c r="C211" t="n">
         <v>42.65999984741211</v>
@@ -6018,7 +6018,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>40.09281539916992</v>
+        <v>40.09280776977539</v>
       </c>
       <c r="C212" t="n">
         <v>42.91999816894531</v>
@@ -6045,7 +6045,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>36.8233642578125</v>
+        <v>36.82336044311523</v>
       </c>
       <c r="C213" t="n">
         <v>39.41999816894531</v>
@@ -6207,7 +6207,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>29.78899574279785</v>
+        <v>29.78899955749512</v>
       </c>
       <c r="C219" t="n">
         <v>31.25</v>
@@ -6234,7 +6234,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>34.43391799926758</v>
+        <v>34.43392181396484</v>
       </c>
       <c r="C220" t="n">
         <v>35.84000015258789</v>
@@ -6261,7 +6261,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>39.04561233520508</v>
+        <v>39.04561614990234</v>
       </c>
       <c r="C221" t="n">
         <v>40.63999938964844</v>
@@ -6288,7 +6288,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>40.29460525512695</v>
+        <v>40.29461288452148</v>
       </c>
       <c r="C222" t="n">
         <v>41.93999862670898</v>
@@ -6342,7 +6342,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>47.42794418334961</v>
+        <v>47.42794036865234</v>
       </c>
       <c r="C224" t="n">
         <v>49.06999969482422</v>
@@ -6396,7 +6396,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>51.91283798217773</v>
+        <v>51.912841796875</v>
       </c>
       <c r="C226" t="n">
         <v>53.45000076293945</v>
@@ -6450,7 +6450,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>40.97631072998047</v>
+        <v>40.97631454467773</v>
       </c>
       <c r="C228" t="n">
         <v>41.93999862670898</v>
@@ -6477,7 +6477,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>36.36477279663086</v>
+        <v>36.36476898193359</v>
       </c>
       <c r="C229" t="n">
         <v>37.22000122070312</v>
@@ -6504,7 +6504,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>41.7383918762207</v>
+        <v>41.73838806152344</v>
       </c>
       <c r="C230" t="n">
         <v>42.72000122070312</v>
@@ -6560,7 +6560,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>47.4506721496582</v>
+        <v>47.45067596435547</v>
       </c>
       <c r="C232" t="n">
         <v>48.27999877929688</v>
@@ -6618,7 +6618,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>52.05698394775391</v>
+        <v>52.05698776245117</v>
       </c>
       <c r="C234" t="n">
         <v>52.72000122070312</v>
@@ -6676,7 +6676,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>61.31901931762695</v>
+        <v>61.31902313232422</v>
       </c>
       <c r="C236" t="n">
         <v>62.09999847412109</v>
@@ -6763,7 +6763,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>80.21762084960938</v>
+        <v>80.21761322021484</v>
       </c>
       <c r="C239" t="n">
         <v>80.97000122070312</v>
@@ -6821,7 +6821,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>99.20967864990234</v>
+        <v>99.20967102050781</v>
       </c>
       <c r="C241" t="n">
         <v>99.84999847412109</v>
